--- a/Chem Lab Data - Copy.xlsx
+++ b/Chem Lab Data - Copy.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECC0E292-1370-4AAA-99A7-F4A1CE59AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shri/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D4CC1E-9383-2E4E-804B-20D7F6A43D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>Table 1: Quantitative Data of mass of copper deposited at cathode over 5 different time intervals during copper electrolysis over a constant current</t>
   </si>
@@ -102,12 +107,6 @@
     <t>Equation</t>
   </si>
   <si>
-    <t>y= (0. ± 0.)x + (0. ± 0.) g/s</t>
-  </si>
-  <si>
-    <t>max fit</t>
-  </si>
-  <si>
     <t>Table 2: Processed data of copper deposited at cathode over 5 different time intervals during copper electrolysis over a constant current</t>
   </si>
   <si>
@@ -115,12 +114,6 @@
   </si>
   <si>
     <t>Average Mass plated (g) ±0.06g</t>
-  </si>
-  <si>
-    <t>min fit</t>
-  </si>
-  <si>
-    <t>theoretical</t>
   </si>
   <si>
     <t>Time t (s) ±1.0s</t>
@@ -140,6 +133,9 @@
   <si>
     <t>Percentage error (%)</t>
   </si>
+  <si>
+    <t>theoretical values</t>
+  </si>
 </sst>
 </file>
 
@@ -152,7 +148,7 @@
     <numFmt numFmtId="167" formatCode="0.00000E+00"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +161,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -179,13 +176,14 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -194,16 +192,17 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,8 +227,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -528,6 +533,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -556,7 +572,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -614,6 +629,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -677,9 +699,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -689,11 +708,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,31 +845,19 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!J16:J17</c:f>
+              <c:f>Sheet1!$J$16:$J$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>239</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>481</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!K16:K17</c:f>
+              <c:f>Sheet1!$K$16:$K$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>2E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-2E-3</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -906,31 +910,19 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!L16:L17</c:f>
+              <c:f>Sheet1!$L$16:$L$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>241</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>479</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!M16:M17</c:f>
+              <c:f>Sheet1!$M$16:$M$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-2E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2E-3</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1365,37 +1357,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1550,31 +1511,19 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!L16:L17</c:f>
+              <c:f>Sheet1!$L$16:$L$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>241</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>479</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!M16:M17</c:f>
+              <c:f>Sheet1!$M$16:$M$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>-2E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2E-3</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1627,31 +1576,19 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!J16:J17</c:f>
+              <c:f>Sheet1!$J$16:$J$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>239</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>481</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!K16:K17</c:f>
+              <c:f>Sheet1!$K$16:$K$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>2E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-2E-3</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1839,7 +1776,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!D25:D29</c:f>
+              <c:f>Sheet1!$D$25:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1863,7 +1800,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!E25:E29</c:f>
+              <c:f>Sheet1!$E$25:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2141,37 +2078,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -3326,15 +3232,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>663575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>596900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3359,65 +3265,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>542925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA73FE67-9038-4283-92D8-7C3B65912086}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{16256955-1255-69A9-BD14-9DAAD466E3DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12992100" y="4324350"/>
-          <a:ext cx="4572000" cy="2647950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3441,7 +3300,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3451,9 +3310,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3491,7 +3350,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3597,7 +3456,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3739,7 +3598,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3748,93 +3607,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:Y30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
+    <col min="22" max="22" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25">
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
-    <row r="2" spans="2:25">
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
     </row>
-    <row r="3" spans="2:25" ht="15" customHeight="1">
-      <c r="B3" s="45" t="s">
+    <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
     </row>
-    <row r="4" spans="2:25">
-      <c r="B4" s="45"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="52" t="s">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B4" s="47"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51" t="s">
+      <c r="E4" s="53"/>
+      <c r="F4" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51" t="s">
+      <c r="G4" s="53"/>
+      <c r="H4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="51"/>
-      <c r="O4" s="35" t="s">
+      <c r="I4" s="53"/>
+      <c r="O4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="37"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="39"/>
     </row>
-    <row r="5" spans="2:25">
-      <c r="B5" s="45"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="10" t="s">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B5" s="47"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -3853,48 +3712,48 @@
         <v>9</v>
       </c>
       <c r="O5" s="2"/>
-      <c r="P5" s="38" t="s">
+      <c r="P5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="39" t="s">
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="41" t="s">
+      <c r="W5" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="43" t="s">
+      <c r="X5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="44"/>
+      <c r="Y5" s="46"/>
     </row>
-    <row r="6" spans="2:25">
-      <c r="B6" s="32">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B6" s="31">
         <v>240</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>0.5</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>1.0509999999999999</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>1.0649999999999999</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>1.0669999999999999</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>1.087</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>1.0609999999999999</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="18">
         <v>1.0820000000000001</v>
       </c>
       <c r="O6" s="2"/>
@@ -3916,8 +3775,8 @@
       <c r="U6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V6" s="40"/>
-      <c r="W6" s="42"/>
+      <c r="V6" s="42"/>
+      <c r="W6" s="44"/>
       <c r="X6" s="3" t="s">
         <v>20</v>
       </c>
@@ -3925,447 +3784,357 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:25">
-      <c r="B7" s="32">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B7" s="31">
         <v>300</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>0.5</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1.0589999999999999</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <v>1.081</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="23">
         <v>1.0429999999999999</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <v>1.0580000000000001</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <v>1.0489999999999999</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="23">
         <v>1.081</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="5">
-        <f>SUM(D16:D20)</f>
-        <v>1800</v>
-      </c>
-      <c r="Q7" s="5">
-        <f>(D16^2+D17^2+D18^2+D19^2+D20^2)</f>
-        <v>684000</v>
-      </c>
-      <c r="R7" s="15">
-        <f>P7^2</f>
-        <v>3240000</v>
-      </c>
-      <c r="S7" s="5">
-        <f>SUM(H16:H20)</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="13">
-        <f>(H16^2+H17^2+H18^2+H20^2+H19^2)</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <f>D16*H16+D17*H17+D18*H18+D19*H19+D20*H20</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="28">
-        <f>(U7-(1/5)*P7*S7)/(Q7-(1/5)*R7)</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="5">
-        <f>(1/5)*(S7-V7*P7)</f>
-        <v>0</v>
-      </c>
-      <c r="X7" s="14">
-        <f>Y7/SQRT(Q7-(1/5)*R7)</f>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="16">
-        <f>SQRT((T7-W7*S7-V7*U7)/3)</f>
-        <v>0</v>
-      </c>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="15"/>
     </row>
-    <row r="8" spans="2:25">
-      <c r="B8" s="32">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B8" s="31">
         <v>360</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>0.5</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>1.0589999999999999</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <v>1.0940000000000001</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="18">
         <v>1.0429999999999999</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <v>1.081</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <v>1.06</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="18">
         <v>1.0840000000000001</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="33" t="s">
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="36"/>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B9" s="31">
+        <v>420</v>
+      </c>
+      <c r="C9" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="21">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="E9" s="18">
+        <v>1.081</v>
+      </c>
+      <c r="F9" s="18">
+        <v>1.0740000000000001</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1.1020000000000001</v>
+      </c>
+      <c r="H9" s="18">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="I9" s="18">
+        <v>1.0960000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B10" s="31">
+        <v>480</v>
+      </c>
+      <c r="C10" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="21">
+        <v>1.0409999999999999</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1.093</v>
+      </c>
+      <c r="F10" s="18">
+        <v>1.048</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1.0920000000000001</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1.052</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="V11" s="24"/>
+    </row>
+    <row r="13" spans="2:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="34"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
     </row>
-    <row r="9" spans="2:25">
-      <c r="B9" s="32">
-        <v>420</v>
-      </c>
-      <c r="C9" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="22">
-        <v>1.0289999999999999</v>
-      </c>
-      <c r="E9" s="19">
-        <v>1.081</v>
-      </c>
-      <c r="F9" s="19">
-        <v>1.0740000000000001</v>
-      </c>
-      <c r="G9" s="19">
-        <v>1.1020000000000001</v>
-      </c>
-      <c r="H9" s="19">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="I9" s="19">
-        <v>1.0960000000000001</v>
-      </c>
+    <row r="14" spans="2:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="58"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="34"/>
     </row>
-    <row r="10" spans="2:25">
-      <c r="B10" s="32">
-        <v>480</v>
-      </c>
-      <c r="C10" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="22">
-        <v>1.0409999999999999</v>
-      </c>
-      <c r="E10" s="19">
-        <v>1.093</v>
-      </c>
-      <c r="F10" s="19">
-        <v>1.048</v>
-      </c>
-      <c r="G10" s="19">
-        <v>1.0920000000000001</v>
-      </c>
-      <c r="H10" s="19">
-        <v>1.052</v>
-      </c>
-      <c r="I10" s="19">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="O10" t="s">
-        <v>24</v>
-      </c>
+    <row r="15" spans="2:25" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="57"/>
+      <c r="E15" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
     </row>
-    <row r="11" spans="2:25">
-      <c r="P11" s="21">
-        <f>SUM(L16:L17)</f>
-        <v>720</v>
-      </c>
-      <c r="Q11" s="21">
-        <f>L16^2+L17^2</f>
-        <v>287522</v>
-      </c>
-      <c r="R11" s="21">
-        <f>P11^2</f>
-        <v>518400</v>
-      </c>
-      <c r="S11" s="21">
-        <f>SUM(M16:M17)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="21">
-        <f>M16^2+M17^2</f>
-        <v>7.9999999999999996E-6</v>
-      </c>
-      <c r="U11">
-        <f>L16*M16+L17*M17</f>
-        <v>0.47600000000000009</v>
-      </c>
-      <c r="V11" s="25">
-        <f>(U11-(1/2)*P11*S11)/(Q11-(1/2)*R11)</f>
-        <v>1.6806722689075634E-5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:25">
-      <c r="Y12">
-        <f>V7/0.00017</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:25" ht="48.75" customHeight="1">
-      <c r="D13" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="2:25" ht="24.75" customHeight="1">
-      <c r="D14" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:25" ht="32.25" customHeight="1">
-      <c r="D15" s="56"/>
-      <c r="E15" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="59"/>
-      <c r="J15" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="54"/>
-    </row>
-    <row r="16" spans="2:25">
-      <c r="D16" s="32">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="D16" s="31">
         <v>240</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="J16" s="7">
-        <v>239</v>
-      </c>
-      <c r="K16" s="7">
-        <f>H16+0.002</f>
-        <v>2E-3</v>
-      </c>
-      <c r="L16" s="7">
-        <v>241</v>
-      </c>
-      <c r="M16" s="7">
-        <f>H16-0.002</f>
-        <v>-2E-3</v>
-      </c>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
     </row>
-    <row r="17" spans="3:13">
-      <c r="D17" s="32">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="D17" s="31">
         <v>300</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="J17" s="7">
-        <v>481</v>
-      </c>
-      <c r="K17" s="7">
-        <f>H20-0.002</f>
-        <v>-2E-3</v>
-      </c>
-      <c r="L17" s="7">
-        <v>479</v>
-      </c>
-      <c r="M17" s="7">
-        <f>H20+0.002</f>
-        <v>2E-3</v>
-      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
     </row>
-    <row r="18" spans="3:13">
-      <c r="D18" s="32">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="D18" s="31">
         <v>360</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
     </row>
-    <row r="19" spans="3:13">
-      <c r="D19" s="32">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="D19" s="31">
         <v>420</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
     </row>
-    <row r="20" spans="3:13">
-      <c r="D20" s="32">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="D20" s="31">
         <v>480</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
     </row>
-    <row r="23" spans="3:13">
-      <c r="C23" s="53" t="s">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C23" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+    </row>
+    <row r="24" spans="3:13" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
+      <c r="H24" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="24" spans="3:13" ht="86.25" customHeight="1">
-      <c r="C24" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>35</v>
-      </c>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C25" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="17">
+        <v>240</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="25"/>
     </row>
-    <row r="25" spans="3:13">
-      <c r="C25" s="27">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C26" s="26">
         <v>0.5</v>
       </c>
-      <c r="D25" s="18">
-        <v>240</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="26"/>
+      <c r="D26" s="17">
+        <v>300</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="25"/>
     </row>
-    <row r="26" spans="3:13">
-      <c r="C26" s="27">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C27" s="26">
         <v>0.5</v>
       </c>
-      <c r="D26" s="18">
-        <v>300</v>
-      </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="26"/>
+      <c r="D27" s="17">
+        <v>360</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="25"/>
     </row>
-    <row r="27" spans="3:13">
-      <c r="C27" s="27">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C28" s="26">
         <v>0.5</v>
       </c>
-      <c r="D27" s="18">
-        <v>360</v>
-      </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="26"/>
+      <c r="D28" s="17">
+        <v>420</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="25"/>
     </row>
-    <row r="28" spans="3:13">
-      <c r="C28" s="27">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="C29" s="26">
         <v>0.5</v>
       </c>
-      <c r="D28" s="18">
-        <v>420</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="26"/>
+      <c r="D29" s="17">
+        <v>480</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="25"/>
     </row>
-    <row r="29" spans="3:13">
-      <c r="C29" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="D29" s="18">
-        <v>480</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="26"/>
-    </row>
-    <row r="30" spans="3:13">
-      <c r="E30" s="17"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="E30" s="16"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="17">
     <mergeCell ref="C23:I23"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:H15"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>

--- a/Chem Lab Data - Copy.xlsx
+++ b/Chem Lab Data - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shri/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D4CC1E-9383-2E4E-804B-20D7F6A43D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C4A204-89BA-1543-A29C-37CAC253F470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Table 1: Quantitative Data of mass of copper deposited at cathode over 5 different time intervals during copper electrolysis over a constant current</t>
   </si>
@@ -59,16 +59,10 @@
     <t>Trial 3</t>
   </si>
   <si>
-    <t>Table : Linear Regression Analysis of mass of copper deposited at cathode over 5 different time intervals during copper electrolysis</t>
-  </si>
-  <si>
     <t>Initial</t>
   </si>
   <si>
     <t>Final</t>
-  </si>
-  <si>
-    <t>sum</t>
   </si>
   <si>
     <t>m (slope)</t>
@@ -78,24 +72,6 @@
   </si>
   <si>
     <t>Errors  δ</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>x^2</t>
-  </si>
-  <si>
-    <t>(sum x)^2</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>y^2</t>
-  </si>
-  <si>
-    <t>xy</t>
   </si>
   <si>
     <t>m</t>
@@ -135,6 +111,9 @@
   </si>
   <si>
     <t>theoretical values</t>
+  </si>
+  <si>
+    <t>Table : Linear Regression Analysis of mass of copper deposited at cathode</t>
   </si>
 </sst>
 </file>
@@ -234,7 +213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -267,48 +246,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -354,19 +291,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -375,79 +299,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -544,51 +395,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -598,117 +460,150 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3618,537 +3513,524 @@
     <col min="7" max="7" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="41.33203125" customWidth="1"/>
     <col min="17" max="17" width="12.33203125" customWidth="1"/>
     <col min="18" max="18" width="10.6640625" customWidth="1"/>
     <col min="22" max="22" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B4" s="47"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="54" t="s">
+    <row r="4" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="30"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53" t="s">
+      <c r="G4" s="36"/>
+      <c r="H4" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="53"/>
-      <c r="O4" s="37" t="s">
+      <c r="I4" s="36"/>
+      <c r="K4" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+    </row>
+    <row r="5" spans="2:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="30"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="39"/>
-    </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B5" s="47"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="55"/>
+      <c r="L5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="40" t="s">
+      <c r="M5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="41" t="s">
+      <c r="N5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y5" s="46"/>
+      <c r="O5" s="64"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B6" s="31">
+      <c r="B6" s="22">
         <v>240</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="18">
         <v>0.5</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="13">
         <v>1.0509999999999999</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="10">
         <v>1.0649999999999999</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="10">
         <v>1.0669999999999999</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="10">
         <v>1.087</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="10">
         <v>1.0609999999999999</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="10">
         <v>1.0820000000000001</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V6" s="42"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="K6" s="56"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B7" s="31">
+      <c r="B7" s="22">
         <v>300</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="18">
         <v>0.5</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="14">
         <v>1.0589999999999999</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="15">
         <v>1.081</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="15">
         <v>1.0429999999999999</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="15">
         <v>1.0580000000000001</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="15">
         <v>1.0489999999999999</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="15">
         <v>1.081</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="15"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="53"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B8" s="31">
+      <c r="B8" s="22">
         <v>360</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="18">
         <v>0.5</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="13">
         <v>1.0589999999999999</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="10">
         <v>1.0940000000000001</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="10">
         <v>1.0429999999999999</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="10">
         <v>1.081</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="10">
         <v>1.06</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="10">
         <v>1.0840000000000001</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="36"/>
+      <c r="K8" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="61"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="63"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B9" s="31">
+      <c r="B9" s="22">
         <v>420</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="18">
         <v>0.5</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="13">
         <v>1.0289999999999999</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="10">
         <v>1.081</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="10">
         <v>1.0740000000000001</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="10">
         <v>1.1020000000000001</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="10">
         <v>1.0660000000000001</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="10">
         <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="B10" s="31">
+      <c r="B10" s="22">
         <v>480</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="18">
         <v>0.5</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="13">
         <v>1.0409999999999999</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="10">
         <v>1.093</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="10">
         <v>1.048</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="10">
         <v>1.0920000000000001</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="10">
         <v>1.052</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="10">
         <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="V11" s="24"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="V11" s="16"/>
     </row>
     <row r="13" spans="2:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D13" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="11"/>
+      <c r="D13" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="2:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="34"/>
+      <c r="E14" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="25"/>
     </row>
     <row r="15" spans="2:25" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="57"/>
-      <c r="E15" s="32" t="s">
+      <c r="D15" s="27"/>
+      <c r="E15" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H15" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
+      <c r="H15" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="D16" s="31">
+      <c r="D16" s="22">
         <v>240</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="D17" s="31">
+      <c r="D17" s="22">
         <v>300</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="D18" s="31">
+      <c r="D18" s="22">
         <v>360</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="D19" s="31">
+      <c r="D19" s="22">
         <v>420</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="D20" s="31">
+      <c r="D20" s="22">
         <v>480</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C23" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
+      <c r="C23" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
     </row>
     <row r="24" spans="3:13" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="30" t="s">
-        <v>31</v>
+      <c r="D24" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C25" s="26">
+      <c r="C25" s="18">
         <v>0.5</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="9">
         <v>240</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="25"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C26" s="26">
+      <c r="C26" s="18">
         <v>0.5</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="9">
         <v>300</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="25"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C27" s="26">
+      <c r="C27" s="18">
         <v>0.5</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="9">
         <v>360</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="25"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C28" s="26">
+      <c r="C28" s="18">
         <v>0.5</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="9">
         <v>420</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="25"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="C29" s="26">
+      <c r="C29" s="18">
         <v>0.5</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="9">
         <v>480</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="25"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.2">
-      <c r="E30" s="16"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="E30" s="8"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="B1:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="B1:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="P8:Y8"/>
-    <mergeCell ref="O4:Y4"/>
-    <mergeCell ref="P5:U5"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:Y5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
